--- a/docs/MARKETPLACE_FORMULA_REFERENCE.xlsx
+++ b/docs/MARKETPLACE_FORMULA_REFERENCE.xlsx
@@ -473,7 +473,7 @@
     <t xml:space="preserve">Postage per leg (postage + its VAT)</t>
   </si>
   <si>
-    <t xml:space="preserve">e.g. £6.30 postage × 1.2. Snapshotted when the return is taken.</t>
+    <t xml:space="preserve">e.g. £6.30 postage × 1.2. Snapshotted when the return is taken. Only the VAT the postage ACTUALLY carried: eBay shipping is zero-rated, so an eBay leg is the bare £4.65 — no VAT added.</t>
   </si>
   <si>
     <t xml:space="preserve">Legs billed (from the table above)</t>
@@ -2588,7 +2588,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>148</v>
       </c>
